--- a/delhi_leads.xlsx
+++ b/delhi_leads.xlsx
@@ -435,20 +435,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,11 +514,15 @@
           <t>Brew Cafe</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>230</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -564,23 +568,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lakeview bistro</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>879</v>
+          <t>Brucha coffee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12b, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+          <t>B 14, DDA MARKET, BB Block, Janakpuri, New Delhi, Delhi, 110058</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>099106 00123</t>
+          <t>096252 96969</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -590,12 +598,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Cafe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lakeview+bistro/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce3002eb45c95:0x48355ab98ee4ea4e!8m2!3d28.5539077!4d77.194598!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEKcmVzdGF1cmFudOABAA!16s%2Fg%2F11xdvsjnsb?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -605,35 +613,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>http://www.kofeynoe.com/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Recycle Cafe</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>160</v>
+          <t>Cafe Dwarka Heights</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50A 2nd Floor, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+          <t>F-692, block-H, Palam Extension, Palam, Ramphal Chowk Rd, Sector 7 Dwarka, Dwarka, Delhi, 110077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>098731 19688</t>
+          <t>011 6136 4449</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -643,12 +655,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Live music bar</t>
+          <t>Cafe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Recycle+Cafe/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d5bff6bea75:0x39c545c9b829eaf!8m2!3d28.5535566!4d77.1941963!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEObGl2ZV9tdXNpY19iYXLgAQA!16s%2Fg%2F11gjkjcvqy?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -658,116 +670,2917 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://cafe.carococoroasters.com/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gypsy Café</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>818</v>
+          <t>Cafe Veda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13 a /ground floor / lakeside, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+          <t>Pardhan Chowk, RZ-169/A, Block C, Sadh Nagar, Palam, New Delhi, Delhi, 110045</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>099905 05529</t>
+          <t>098056 55013</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.swiggy.com/restaurants/gypsy-cafe-hauz-khas-vikaspuri-delhi-678381/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cafe</t>
+          <t>Coffee shop</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Gypsy+Caf%C3%A9/@28.5544717,77.1846342,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d8a843af0fb:0x8fe97d6dd9444d5a!8m2!3d28.5544138!4d77.1940607!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEEY2FmZeABAA!16s%2Fg%2F11gbx9wm_p?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[MEDIUM] Medium</t>
+          <t>[HIGH] High</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>http://www.shellbeacon.com/</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Cafe YNM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6, Palam Village Rd, Block RZ, Raj Nagar I, Raj Nagar, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>099113 44818</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cafe b1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rajendra Arihant Tower, Dharam Marg, b1, B1 Market, Pocket B 1, Super Bazar, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>098718 94877</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Café Tree</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>305C Block C5, Janakpuri, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Caf%C3%A9+Tree/@28.6422947,76.9539243,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d05f86d81cc61:0x597c39667a05be81!8m2!3d28.6157089!4d77.0942156!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11tmvtkqq7?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>City Hot Cafe</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shop No A, 1/16, Metro Station, Dabri - Palam Rd, near by Dashrath Puri, Block B, Vijay Enclave, Mahavir Enclave, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>099904 56100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Coffee Club Cafe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C-305, Palam Extension Sector 7, Dwarka, Ramphal Chowk Rd, near MiniSo, opp. Vishal Mega Mart Lane, Area, New Delhi, Delhi 110075</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>098118 18053</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cottage cafe by La Polo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>46, Tolstoy Rd, Atul Grove Road, Connaught Place, New Delhi, Delhi 110001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>081302 14666</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Deja bru cafe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ganesh Nagar, Shivaji Marg, B2A Block, Block B 2B, Janakpuri, New Delhi, Delhi 110058</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070420 89484</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Deja+bru+cafe/@28.6209996,76.9287952,12z/data=!4m10!1m2!2m1!1scafes+in+Delhi!3m6!1s0x390d0509124768f9:0xbe6f4d5620a31e20!8m2!3d28.633734!4d77.0902051!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBC2NvZmZlZV9zaG9w4AEA!16s%2Fg%2F11n07g9b8l?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dolci Patisserie And Cafe</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>22, A3 Block Rd, Block A3, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>085878 88840</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Dolci+Patisserie+And+Cafe/@28.6209996,76.9287952,12z/data=!4m10!1m2!2m1!1scafes+in+Delhi!3m6!1s0x390d05eb9290aa9b:0xde35c536973546e3!8m2!3d28.6209996!4d77.0812305!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11l5tn2xj6?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>KOFEYNOE | Best Coffee House in Delhi</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>http://www.kofeynoe.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DownTown Cafe</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>H3PC+WMR, Block G, Sector 7 Dwarka, Dwarka, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070602 42618</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Echoes</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>E-1, Major Sudesh Kumar Marg, Block E, Rajouri Garden, New Delhi, Delhi, 110027</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>087439 96500</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Echoes/@28.633734,76.9377698,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d0325c5ba6de3:0x6830a47ee35b0890!8m2!3d28.6421909!4d77.1238676!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11trrkwxp2?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kartoon Cafe Rajouri Garden</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>J-2, 12, Block J, Rajouri Garden, New Delhi, Delhi, 110027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>098736 61133</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>King wolf cafe</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>market, Rohini Sector 9, Sector 9, DC chowk, New delhi, Delhi, 110085</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>The Bun - Chai Cafe</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://the-bun-chai-cafe.grexa.site/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Krishna Rooftop Cafe</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Top Floor, Tooti Chowk, 659, Main Bazar Rd, Bazar Sangatrashan, Main Bazar, Kaseru Walan, Paharganj, New Delhi, Delhi 110055</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>093102 73053</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Krishna+Rooftop+Cafe/@28.641161,77.0612152,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390cfd43e30e7cb5:0x7d91081ee8e8893d!8m2!3d28.641161!4d77.2136505!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F12q4x48x2?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lakeview bistro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>12b, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>099106 00123</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Lakeview+bistro/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce3002eb45c95:0x48355ab98ee4ea4e!8m2!3d28.5539077!4d77.194598!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEKcmVzdGF1cmFudOABAA!16s%2Fg%2F11xdvsjnsb?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Moonlight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>on, DEEN DAYAL UPADHYAY HOSPITAL, C -Block, road, Hari Nagar, New Delhi, Delhi 110064</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>095400 07160</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Cafe West Delhi</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>http://www.cafewestdelhi.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ninewatt coffee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gopinath Bldg Rd, Gopi Nath Bazar, Delhi Cantonment, New Delhi, Delhi 110010</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>097100 03099</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Old door cafe lounge and Hooka</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>E-1088 , Palam Extn, Ramphal Chowk Rd, Block F, Sector 7 Dwarka, Dwarka, New Delhi, Delhi 110077</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hookah bar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pocket Friendly Cafe</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>gate no 1, K9 BK Dutt Colony, Jor Bagh, New Delhi, Delhi 110003</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>084472 41849</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pocket friendly cafe</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>H3GH+FWH, Street Number 1, Block P, Raj Nagar II Extension, Raj Nagar, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q Bistro Café and Patisserie</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Block C4, D/ 56-A, C4G, Block C4G, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>011 4370 1014</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Modern French restaurant</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Q+Bistro+Caf%C3%A9+and+Patisserie/@28.6422947,76.9539243,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d04bac3eb3275:0x19a8289004cb126c!8m2!3d28.6179699!4d77.0944172!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBGG1vZGVybl9mcmVuY2hfcmVzdGF1cmFudOABAA!16s%2Fg%2F11b7hrjq6m?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Re Fuel Cafe</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Old Mehrauli Rd, Block B, Raj Nagar I, Raj Nagar, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>099672 54230</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Recycle Cafe</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>50A 2nd Floor, Hauz Khas Fort Rd, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>098731 19688</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Live music bar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Recycle+Cafe/@28.5535955,77.1846895,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d5bff6bea75:0x39c545c9b829eaf!8m2!3d28.5535566!4d77.1941963!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEObGl2ZV9tdXNpY19iYXLgAQA!16s%2Fg%2F11gjkjcvqy?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Spaced Out Cafe</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4A , 2nd Floor, Shahpur Jat, New Delhi, Delhi 110017</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>092055 47663</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>The Flavour's Cafe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A-3/A, Gurudwara Rd, Mahavir Enclave I, Mahavir Enclave Part 1, Mahavir Enclave, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>088588 62921</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>The Green Cafe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>D-2/54, Rithala Rd, Kalu Colony, Harshdev Colony, Pocket B, Budh Vihar Phase II, Budh Vihar, Delhi, 110085</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The Pink Room</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>29 A, 2nd Floor, Hauz Khas village, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Pink+Room/@28.5541607,77.1849383,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d8a9e714a45:0x78d480b18e2c4250!8m2!3d28.5541607!4d77.1944655!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEDYmFy4AEA!16s%2Fg%2F124t08zvf?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The Study Cafe</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>First Floor, Hotel Neelgagan, Wz-80A, Mohan Nagar, Main, Pankha Rd, New Delhi, Delhi 110046</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>097110 29902</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The nukkad cafe</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C-924 palam extension, Ramphal Chowk Rd, Block C, Sector 7 Dwarka, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>096439 69168</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WestSyd cafe</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Community Centre, B1-53, B1 Market, Pocket B 1, Super Bazar, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>011 3689 9658</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/WestSyd+cafe/@28.6301179,76.9382403,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d0567693d56b1:0x8185a4f926b7d348!8m2!3d28.6301179!4d77.0906756!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11x0cf0vg3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[HIGH] High</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>IKVITI - Coffee Roasters &amp; Gourmet Kitchen</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>http://www.ikviti.coffee/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cafe Olives 51</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ramphal Chowk, E-1089, Block E, Sector 7 Dwarka, Dwarka, New Delhi, Delhi, 110075</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>080105 73627</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-olives-51-palam-dwarka2-delhi-35261/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Sardar+Saab+Cafe+%7C+Hauz+Khaz/@28.6517105,76.9748118,12z/data=!3m1!5s0x390ce20d0fe82687:0x2b85af776090ae13!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce36e118dba61:0x10f65126e31940e1!8m2!3d28.5504659!4d77.2044369!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11f61pp6_6?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cafe Punjab -Best Restaurant in Subhash Nagar-Best Cafe in West Delhi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4/13, Subash Nagar Marg, Block 17, Block 4, Subhash Nagar, New Delhi, Delhi, 110064</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>092682 04203</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/punjab-cafe-subhash-nagar-koramangala-delhi-1023178/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cafe Stela</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Block B2B, Cafe Stela, 24/17, B1 Rd, Chhoti Subji Mandi, Janakpuri, New Delhi, Delhi, 110058</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>079821 90457</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cafe_stela?igshid=NzNkNDdiOGI=</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cafe+Stela/@28.7081957,76.9520156,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d052960368037:0x9d712fef2f64c649!8m2!3d28.633834!4d77.0944652!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11s8k95h7h?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>http://www.shellbeacon.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cafe Ten</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plot 13, Odeon Plaza 2, Shop 109, 1st Floor, above Citi Bank Atm, Sector 10 Dwarka, Dwarka, New Delhi, Delhi 110075</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>093117 61176</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-ten-dwarka-delhi-322264/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cafe+Ten/@28.5836629,76.9347208,12z/data=!3m1!5s0x390d1b206106fca1:0x9d4e494ec51387f8!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d1b343e1da4b5:0x17f386cf8aaf73f1!8m2!3d28.5905942!4d77.0575952!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11qld_w2f5?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cafe Trio</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ram Chowk, RZ-150/1, Street Number 2, P Block, Sadh Nagar, Palam, New Delhi, Delhi, 110045</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>096435 51414</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-trio-dwarka-delhi-1359117/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cafe YNM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A-2, MAIN PALAM DABRI ROAD, MAHAVIR ENCLAVE, PALAM, Dwarka, New Delhi, Delhi 110045</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>088514 29306</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/cafe-ynm-mahavir-enclave-dwarka-koramangala-delhi-1042208/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Friends Cafe</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Metro Station, A-10, Ramdutt Enclave, near Lal Mandir, Uttam Nagar East, New Delhi, Delhi 110059</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>089503 93361</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/friends-cafe-ram-datta-enclave-uttam-nagar-delhi-713664/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BYTERRA - A Conscious Cafe</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>http://www.byterra.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guliyano Cafe</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>863, Joshi Path, Block A, Karol Bagh, New Delhi, Delhi, 110005</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>092125 08354</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.zomato.com/Guliyano2/menu</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Guliyano+Cafe/@28.5475066,77.0920603,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390cfd6388d11ccb:0x34b4e6c6fef08df!8m2!3d28.6532984!4d77.1998514!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11f1zlcd9z?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gypsy Café</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13 a /ground floor / lakeside, Hauz Khas Village, Deer Park, Hauz Khas, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>099905 05529</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/gypsy-cafe-hauz-khas-vikaspuri-delhi-678381/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Gypsy+Caf%C3%A9/@28.5544717,77.1846342,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390d1d8a843af0fb:0x8fe97d6dd9444d5a!8m2!3d28.5544138!4d77.1940607!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgEEY2FmZeABAA!16s%2Fg%2F11gbx9wm_p?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ShellBeacon Cafe, Bar &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>http://www.shellbeacon.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Josie's Coffee House</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Shop No. 3, Ground Floor, Central, beside La Pino's Pizza, Old Rajender Nagar market, Block 55, Rajinder Nagar, New Delhi, Delhi, 110060</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>096677 79071</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/josies-coffee-house-rajinder-nagar-karol-bagh-east-patel-nagar-delhi-375547/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Josie's+Coffee+House/@28.6301179,76.9382403,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03295c656cab:0xc932eb8a70668def!8m2!3d28.6417586!4d77.1853622!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBCnJlc3RhdXJhbnTgAQA!16s%2Fg%2F11h_ftcn_b?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mudra Cafe &amp; Lounge</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Metro Station, RZ-I/13, Main Rd, above Palam Dominos, near Palam, Palam Colony, Raj Nagar I, Palam, New Delhi, Delhi, 110077</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>093105 69922</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/mudra-cafe-and-lounge-dwarka-delhi-998907/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rajouri House Cafe &amp; Restro</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>above NYKAA Trends showroom, F-122, Highstreet, Main Market, Rajouri Garden, New Delhi, Delhi 110027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>077018 99219</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://link.zomato.com/xqzv/rshare?id=6216205430563ff3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Rajouri+House+Cafe+%26+Restro/@28.6441705,76.9696324,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03dc42d7191d:0x65fb4ff7a30e4061!8m2!3d28.6441705!4d77.1220677!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11vj35knz1?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sehat Cafe</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>opposite Shiksha Bharti School Road, Block C, Palam Extension, Palam, New Delhi, Delhi, 110075</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>093191 24442</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/sehat-cafe-sector-7-dwarka2-delhi-76780/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Seven Seeds Coffee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5, Block W, Arjun Nagar, Green Park, New Delhi, Delhi 110016</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>099718 66227</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/7-seeds-coffee-green-park-vikaspuri-delhi-928704/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Simpy's Cafe The Best family Restaurant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CE 3 HARI NAGAR CLOCK TOWER, New Delhi, Delhi 110064</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>088516 09140</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/simpys-hari-nagar-koramangala-delhi-1351276/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Simpy's+Cafe+The+Best+family+Restaurant/@28.6422947,76.9539243,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d03369e1d6929:0x9d64a751a5092ff4!8m2!3d28.6253711!4d77.1110034!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11nnpp4g5k?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Cafe West Delhi</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>http://www.cafewestdelhi.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Tan Coffee | Hauz Khas, Delhi</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>385</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Shop No 8 &amp; 9, Surya Mansion, 1, Chaudhary Dilip Singh Marg, Kaushalya Park, Padmini Enclave, Hauz Khas, New Delhi, Delhi 110016</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>091666 63389</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://www.instagram.com/tancoffeeindia/</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Coffee shop</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Tan+Coffee+%7C+Hauz+Khas,+Delhi/@28.5530484,77.1982965,16z/data=!4m11!1m3!2m2!1scafes+in+Hauz+Khas+Delhi!6e5!3m6!1s0x390ce36d29b7767b:0xcb1f60e473a3a07d!8m2!3d28.5505264!4d77.2045074!15sChhjYWZlcyBpbiBIYXV6IEtoYXMgRGVsaGlaGiIYY2FmZXMgaW4gaGF1eiBraGFzIGRlbGhpkgELY29mZmVlX3Nob3DgAQA!16s%2Fg%2F11shwprtbf?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>[MEDIUM] Medium</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tan Coffee | Prashant Vihar, Delhi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Block-B, Prashant Vihar, Sector 14, Rohini, New Delhi, Delhi, 110085</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>098211 09817</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tancoffeeindia/</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Coffee shop</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tan+Coffee+%7C+Prashant+Vihar,+Delhi/@28.6446478,76.9938964,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d010004e97021:0x68758a07219f42ca!8m2!3d28.7108298!4d77.1331257!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBC2NvZmZlZV9zaG9w4AEA!16s%2Fg%2F11vk6lpll8?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>The BlackFox Cafe</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Shop No 2, DDA Market, Hari Enclave, Hari Nagar, New Delhi, Delhi, 110064</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>088601 99996</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com/restaurants/the-blackfox-cafe-hari-nagar-vikaspuri-delhi-740040/dineout?is_retargeting=true&amp;media_source=GoogleReserve&amp;utm_campaign=GoogleMap&amp;utm_source=GoogleReserve</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fast food restaurant</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>The Daily Dose Cafe</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SHOP AT PLOT A1/1, BLK A1, AMAR SINGH GAHLOT CHOWK, Dwarka Mor, Block B, Sewak Park, Dwarka, New Delhi, Delhi, 110059</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>090132 83706</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://link.zomato.com/xqzv/rshare?id=11286629130563f66</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sukoon Coffee Cafe | Best Specialty Coffee in Delhi</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://cafe.carococoroasters.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Bites And Brew - Cafe and Diner (Vikaspuri)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B, 50, Krishna Park Rd, Block-B, Shankar Garden, Vikaspuri, New Delhi, Delhi, 110018</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>095820 25050</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://zoma.to/r/19201577</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Coast+Caf%C3%A9/@28.6341679,77.0678361,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390ce2757a715595:0xed48c1e0d569e3d0!8m2!3d28.5548163!4d77.1951945!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F1q5hsk2f3?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Soul Pantry - Andaz Delhi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Gate No. 5, Andaz Delhi, Asset, Street Number 1, Aerocity, New Delhi, Delhi 110037</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>085888 04222</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.hyatt.com/andaz/delaz-andaz-delhi/dining</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Soul+Pantry+-+Andaz+Delhi/@28.6446478,76.9938964,12z/data=!4m11!1m3!2m2!1scafes+in+Delhi!6e5!3m6!1s0x390d1df00c45d56d:0xc58a108f30b8bea5!8m2!3d28.5537733!4d77.1223716!15sCg5jYWZlcyBpbiBEZWxoaVoQIg5jYWZlcyBpbiBkZWxoaZIBBGNhZmXgAQA!16s%2Fg%2F11h6lp1vhl?entry=ttu&amp;g_ep=EgoyMDI2MDYxMC4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[LOW] Low</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
